--- a/submissions/08-nutrition-panel-granola/inputs/formula_ocb_26_03.xlsx
+++ b/submissions/08-nutrition-panel-granola/inputs/formula_ocb_26_03.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CAF009-5E45-4F49-9807-FFA7510B0016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07C31D6-C92D-6B4F-B142-C80472866BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formula" sheetId="1" r:id="rId1"/>
@@ -587,7 +587,7 @@
     <col min="5" max="5" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,11 +748,11 @@
         <v>25</v>
       </c>
       <c r="C12" s="3">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.04925</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -820,11 +820,11 @@
         <v>34</v>
       </c>
       <c r="C16" s="3">
-        <v>0.72</v>
+        <v>0.81</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>0.006</v>
+        <v>0.00675</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -875,7 +875,7 @@
     <col min="3" max="3" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>

--- a/submissions/08-nutrition-panel-granola/inputs/formula_ocb_26_03.xlsx
+++ b/submissions/08-nutrition-panel-granola/inputs/formula_ocb_26_03.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07C31D6-C92D-6B4F-B142-C80472866BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B8DA09-FC99-0B4D-8DFF-67D5A9F0994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,11 +622,11 @@
         <v>8</v>
       </c>
       <c r="C5" s="3">
-        <v>39.6</v>
+        <v>37.8</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" ref="D5:D17" si="0">C5/$C$18</f>
-        <v>0.33</v>
+        <v>0.315</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -748,11 +748,11 @@
         <v>25</v>
       </c>
       <c r="C12" s="3">
-        <v>5.91</v>
+        <v>9.12</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>0.04925</v>
+        <v>0.076</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -766,11 +766,11 @@
         <v>27</v>
       </c>
       <c r="C13" s="3">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>0.045</v>
+        <v>0.033333333</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -820,11 +820,11 @@
         <v>34</v>
       </c>
       <c r="C16" s="3">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>0.00675</v>
+        <v>0.006666667</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -948,7 +948,7 @@
         <v>52</v>
       </c>
       <c r="B9">
-        <v>2548</v>
+        <v>2520</v>
       </c>
       <c r="C9" t="s">
         <v>53</v>
